--- a/Tables/G_SkillSaleInfoTable.xlsx
+++ b/Tables/G_SkillSaleInfoTable.xlsx
@@ -355,9 +355,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.38"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
-    <col customWidth="1" min="9" max="9" width="12.63"/>
+    <col customWidth="1" min="1" max="26" width="12.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12020,8 +12018,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.38"/>
-    <col customWidth="1" min="2" max="9" width="12.63"/>
+    <col customWidth="1" min="1" max="26" width="12.88"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Tables/G_SkillSaleInfoTable.xlsx
+++ b/Tables/G_SkillSaleInfoTable.xlsx
@@ -28592,15 +28592,15 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>0</v>
       </c>
       <c r="K2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>-1</v>
       </c>
       <c r="L2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>1</v>
       </c>
       <c r="M2" s="12">
@@ -45738,15 +45738,15 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>100000000</v>
       </c>
       <c r="K2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>99999999</v>
       </c>
       <c r="L2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>100000001</v>
       </c>
       <c r="M2" s="12">

--- a/Tables/G_SkillSaleInfoTable.xlsx
+++ b/Tables/G_SkillSaleInfoTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>식별자 범위</t>
   </si>
@@ -58,6 +58,21 @@
   </si>
   <si>
     <t>대분류(11) + 중분류(10) + 소분류(100) + 베리에이션(21) =&gt; 1,101,010,021</t>
+  </si>
+  <si>
+    <t>가격 타입</t>
+  </si>
+  <si>
+    <t>광고</t>
+  </si>
+  <si>
+    <t>결제</t>
+  </si>
+  <si>
+    <t>아이템</t>
+  </si>
+  <si>
+    <t>스킬</t>
   </si>
   <si>
     <t>Description</t>
@@ -844,7 +859,9 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -872,8 +889,12 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.0</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -900,8 +921,12 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1.0</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -928,8 +953,12 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2.0</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -956,8 +985,12 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>3.0</v>
+      </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -28511,52 +28544,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="7"/>
       <c r="R1" s="9"/>
@@ -28579,7 +28612,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B2" s="10">
         <v>0.0</v>
@@ -46664,52 +46697,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="7"/>
       <c r="R1" s="9"/>
@@ -46730,7 +46763,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B2" s="16">
         <v>1.0</v>

--- a/Tables/G_SkillSaleInfoTable.xlsx
+++ b/Tables/G_SkillSaleInfoTable.xlsx
@@ -114,7 +114,7 @@
     <t>PriceType_01</t>
   </si>
   <si>
-    <t>Kinds_01</t>
+    <t>PriceKinds_01</t>
   </si>
   <si>
     <t>Price_01</t>
@@ -28536,7 +28536,7 @@
     <col customWidth="1" min="10" max="10" width="11.5"/>
     <col customWidth="1" min="11" max="12" width="15.0"/>
     <col customWidth="1" min="13" max="13" width="11.25"/>
-    <col customWidth="1" min="14" max="14" width="8.0"/>
+    <col customWidth="1" min="14" max="14" width="11.75"/>
     <col customWidth="1" min="15" max="15" width="7.63"/>
     <col customWidth="1" min="16" max="16" width="11.0"/>
     <col customWidth="1" min="17" max="34" width="12.88"/>
@@ -28582,7 +28582,7 @@
       <c r="M1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="O1" s="7" t="s">
@@ -46689,10 +46689,10 @@
     <col customWidth="1" min="10" max="10" width="11.5"/>
     <col customWidth="1" min="11" max="12" width="15.0"/>
     <col customWidth="1" min="13" max="13" width="11.25"/>
-    <col customWidth="1" min="14" max="14" width="8.0"/>
+    <col customWidth="1" min="14" max="14" width="11.75"/>
     <col customWidth="1" min="15" max="15" width="7.63"/>
     <col customWidth="1" min="16" max="16" width="11.0"/>
-    <col customWidth="1" min="17" max="32" width="12.88"/>
+    <col customWidth="1" min="17" max="34" width="12.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46735,7 +46735,7 @@
       <c r="M1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="O1" s="7" t="s">
@@ -46760,6 +46760,8 @@
       <c r="AD1" s="4"/>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
@@ -46825,6 +46827,8 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="4"/>
@@ -46859,6 +46863,8 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="4"/>
@@ -46893,6 +46899,8 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="4"/>
@@ -46927,6 +46935,8 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="4"/>
@@ -46961,6 +46971,8 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="4"/>
@@ -46995,6 +47007,8 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
+      <c r="AG7" s="4"/>
+      <c r="AH7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="4"/>
@@ -47029,6 +47043,8 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="4"/>
@@ -47063,6 +47079,8 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="4"/>
@@ -47097,6 +47115,8 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="4"/>
@@ -47131,6 +47151,8 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="4"/>
@@ -47165,6 +47187,8 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="4"/>
@@ -47199,6 +47223,8 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="4"/>
@@ -47233,6 +47259,8 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
+      <c r="AH14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="4"/>
@@ -47267,6 +47295,8 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
+      <c r="AG15" s="4"/>
+      <c r="AH15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="4"/>
@@ -47301,6 +47331,8 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
+      <c r="AG16" s="4"/>
+      <c r="AH16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="4"/>
@@ -47335,6 +47367,8 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="4"/>
@@ -47369,6 +47403,8 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="4"/>
@@ -47403,6 +47439,8 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
+      <c r="AG19" s="4"/>
+      <c r="AH19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="4"/>
@@ -47437,6 +47475,8 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
+      <c r="AG20" s="4"/>
+      <c r="AH20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="4"/>
@@ -47471,6 +47511,8 @@
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
+      <c r="AG21" s="4"/>
+      <c r="AH21" s="4"/>
     </row>
     <row r="22">
       <c r="A22" s="4"/>
@@ -47505,6 +47547,8 @@
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
+      <c r="AG22" s="4"/>
+      <c r="AH22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="4"/>
@@ -47539,6 +47583,8 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="4"/>
@@ -47573,6 +47619,8 @@
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="4"/>
@@ -47607,6 +47655,8 @@
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="4"/>
@@ -47641,6 +47691,8 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="4"/>
@@ -47675,6 +47727,8 @@
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
+      <c r="AG27" s="4"/>
+      <c r="AH27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="4"/>
@@ -47709,6 +47763,8 @@
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="4"/>
@@ -47743,6 +47799,8 @@
       <c r="AD29" s="4"/>
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
     </row>
     <row r="30">
       <c r="A30" s="4"/>
@@ -47777,6 +47835,8 @@
       <c r="AD30" s="4"/>
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
     </row>
     <row r="31">
       <c r="A31" s="4"/>
@@ -47811,6 +47871,8 @@
       <c r="AD31" s="4"/>
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
     </row>
     <row r="32">
       <c r="A32" s="4"/>
@@ -47845,6 +47907,8 @@
       <c r="AD32" s="4"/>
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="4"/>
@@ -47879,6 +47943,8 @@
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
     </row>
     <row r="34">
       <c r="A34" s="4"/>
@@ -47913,6 +47979,8 @@
       <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="4"/>
@@ -47947,6 +48015,8 @@
       <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
+      <c r="AG35" s="4"/>
+      <c r="AH35" s="4"/>
     </row>
     <row r="36">
       <c r="A36" s="4"/>
@@ -47981,6 +48051,8 @@
       <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
+      <c r="AG36" s="4"/>
+      <c r="AH36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="4"/>
@@ -48015,6 +48087,8 @@
       <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
+      <c r="AG37" s="4"/>
+      <c r="AH37" s="4"/>
     </row>
     <row r="38">
       <c r="A38" s="4"/>
@@ -48049,6 +48123,8 @@
       <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
     </row>
     <row r="39">
       <c r="A39" s="4"/>
@@ -48083,6 +48159,8 @@
       <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
     </row>
     <row r="40">
       <c r="A40" s="4"/>
@@ -48117,6 +48195,8 @@
       <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="4"/>
     </row>
     <row r="41">
       <c r="A41" s="4"/>
@@ -48151,6 +48231,8 @@
       <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
     </row>
     <row r="42">
       <c r="A42" s="4"/>
@@ -48185,6 +48267,8 @@
       <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
     </row>
     <row r="43">
       <c r="A43" s="4"/>
@@ -48219,6 +48303,8 @@
       <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
     </row>
     <row r="44">
       <c r="A44" s="4"/>
@@ -48253,6 +48339,8 @@
       <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
     </row>
     <row r="45">
       <c r="A45" s="4"/>
@@ -48287,6 +48375,8 @@
       <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
     </row>
     <row r="46">
       <c r="A46" s="4"/>
@@ -48321,6 +48411,8 @@
       <c r="AD46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
+      <c r="AG46" s="4"/>
+      <c r="AH46" s="4"/>
     </row>
     <row r="47">
       <c r="A47" s="4"/>
@@ -48355,6 +48447,8 @@
       <c r="AD47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
+      <c r="AG47" s="4"/>
+      <c r="AH47" s="4"/>
     </row>
     <row r="48">
       <c r="A48" s="4"/>
@@ -48389,6 +48483,8 @@
       <c r="AD48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
+      <c r="AG48" s="4"/>
+      <c r="AH48" s="4"/>
     </row>
     <row r="49">
       <c r="A49" s="4"/>
@@ -48423,6 +48519,8 @@
       <c r="AD49" s="4"/>
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
     </row>
     <row r="50">
       <c r="A50" s="4"/>
@@ -48457,6 +48555,8 @@
       <c r="AD50" s="4"/>
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
+      <c r="AG50" s="4"/>
+      <c r="AH50" s="4"/>
     </row>
     <row r="51">
       <c r="A51" s="4"/>
@@ -48491,6 +48591,8 @@
       <c r="AD51" s="4"/>
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
+      <c r="AG51" s="4"/>
+      <c r="AH51" s="4"/>
     </row>
     <row r="52">
       <c r="A52" s="4"/>
@@ -48525,6 +48627,8 @@
       <c r="AD52" s="4"/>
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
+      <c r="AG52" s="4"/>
+      <c r="AH52" s="4"/>
     </row>
     <row r="53">
       <c r="A53" s="4"/>
@@ -48559,6 +48663,8 @@
       <c r="AD53" s="4"/>
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
+      <c r="AG53" s="4"/>
+      <c r="AH53" s="4"/>
     </row>
     <row r="54">
       <c r="A54" s="4"/>
@@ -48593,6 +48699,8 @@
       <c r="AD54" s="4"/>
       <c r="AE54" s="4"/>
       <c r="AF54" s="4"/>
+      <c r="AG54" s="4"/>
+      <c r="AH54" s="4"/>
     </row>
     <row r="55">
       <c r="A55" s="4"/>
@@ -48627,6 +48735,8 @@
       <c r="AD55" s="4"/>
       <c r="AE55" s="4"/>
       <c r="AF55" s="4"/>
+      <c r="AG55" s="4"/>
+      <c r="AH55" s="4"/>
     </row>
     <row r="56">
       <c r="A56" s="4"/>
@@ -48661,6 +48771,8 @@
       <c r="AD56" s="4"/>
       <c r="AE56" s="4"/>
       <c r="AF56" s="4"/>
+      <c r="AG56" s="4"/>
+      <c r="AH56" s="4"/>
     </row>
     <row r="57">
       <c r="A57" s="4"/>
@@ -48695,6 +48807,8 @@
       <c r="AD57" s="4"/>
       <c r="AE57" s="4"/>
       <c r="AF57" s="4"/>
+      <c r="AG57" s="4"/>
+      <c r="AH57" s="4"/>
     </row>
     <row r="58">
       <c r="A58" s="4"/>
@@ -48729,6 +48843,8 @@
       <c r="AD58" s="4"/>
       <c r="AE58" s="4"/>
       <c r="AF58" s="4"/>
+      <c r="AG58" s="4"/>
+      <c r="AH58" s="4"/>
     </row>
     <row r="59">
       <c r="A59" s="4"/>
@@ -48763,6 +48879,8 @@
       <c r="AD59" s="4"/>
       <c r="AE59" s="4"/>
       <c r="AF59" s="4"/>
+      <c r="AG59" s="4"/>
+      <c r="AH59" s="4"/>
     </row>
     <row r="60">
       <c r="A60" s="4"/>
@@ -48797,6 +48915,8 @@
       <c r="AD60" s="4"/>
       <c r="AE60" s="4"/>
       <c r="AF60" s="4"/>
+      <c r="AG60" s="4"/>
+      <c r="AH60" s="4"/>
     </row>
     <row r="61">
       <c r="A61" s="4"/>
@@ -48831,6 +48951,8 @@
       <c r="AD61" s="4"/>
       <c r="AE61" s="4"/>
       <c r="AF61" s="4"/>
+      <c r="AG61" s="4"/>
+      <c r="AH61" s="4"/>
     </row>
     <row r="62">
       <c r="A62" s="4"/>
@@ -48865,6 +48987,8 @@
       <c r="AD62" s="4"/>
       <c r="AE62" s="4"/>
       <c r="AF62" s="4"/>
+      <c r="AG62" s="4"/>
+      <c r="AH62" s="4"/>
     </row>
     <row r="63">
       <c r="A63" s="4"/>
@@ -48899,6 +49023,8 @@
       <c r="AD63" s="4"/>
       <c r="AE63" s="4"/>
       <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+      <c r="AH63" s="4"/>
     </row>
     <row r="64">
       <c r="A64" s="4"/>
@@ -48933,6 +49059,8 @@
       <c r="AD64" s="4"/>
       <c r="AE64" s="4"/>
       <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+      <c r="AH64" s="4"/>
     </row>
     <row r="65">
       <c r="A65" s="4"/>
@@ -48967,6 +49095,8 @@
       <c r="AD65" s="4"/>
       <c r="AE65" s="4"/>
       <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
     </row>
     <row r="66">
       <c r="A66" s="4"/>
@@ -49001,6 +49131,8 @@
       <c r="AD66" s="4"/>
       <c r="AE66" s="4"/>
       <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+      <c r="AH66" s="4"/>
     </row>
     <row r="67">
       <c r="A67" s="4"/>
@@ -49035,6 +49167,8 @@
       <c r="AD67" s="4"/>
       <c r="AE67" s="4"/>
       <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
     </row>
     <row r="68">
       <c r="A68" s="4"/>
@@ -49069,6 +49203,8 @@
       <c r="AD68" s="4"/>
       <c r="AE68" s="4"/>
       <c r="AF68" s="4"/>
+      <c r="AG68" s="4"/>
+      <c r="AH68" s="4"/>
     </row>
     <row r="69">
       <c r="A69" s="4"/>
@@ -49103,6 +49239,8 @@
       <c r="AD69" s="4"/>
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
+      <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
     </row>
     <row r="70">
       <c r="A70" s="4"/>
@@ -49137,6 +49275,8 @@
       <c r="AD70" s="4"/>
       <c r="AE70" s="4"/>
       <c r="AF70" s="4"/>
+      <c r="AG70" s="4"/>
+      <c r="AH70" s="4"/>
     </row>
     <row r="71">
       <c r="A71" s="4"/>
@@ -49171,6 +49311,8 @@
       <c r="AD71" s="4"/>
       <c r="AE71" s="4"/>
       <c r="AF71" s="4"/>
+      <c r="AG71" s="4"/>
+      <c r="AH71" s="4"/>
     </row>
     <row r="72">
       <c r="A72" s="4"/>
@@ -49205,6 +49347,8 @@
       <c r="AD72" s="4"/>
       <c r="AE72" s="4"/>
       <c r="AF72" s="4"/>
+      <c r="AG72" s="4"/>
+      <c r="AH72" s="4"/>
     </row>
     <row r="73">
       <c r="A73" s="4"/>
@@ -49239,6 +49383,8 @@
       <c r="AD73" s="4"/>
       <c r="AE73" s="4"/>
       <c r="AF73" s="4"/>
+      <c r="AG73" s="4"/>
+      <c r="AH73" s="4"/>
     </row>
     <row r="74">
       <c r="A74" s="4"/>
@@ -49273,6 +49419,8 @@
       <c r="AD74" s="4"/>
       <c r="AE74" s="4"/>
       <c r="AF74" s="4"/>
+      <c r="AG74" s="4"/>
+      <c r="AH74" s="4"/>
     </row>
     <row r="75">
       <c r="A75" s="4"/>
@@ -49307,6 +49455,8 @@
       <c r="AD75" s="4"/>
       <c r="AE75" s="4"/>
       <c r="AF75" s="4"/>
+      <c r="AG75" s="4"/>
+      <c r="AH75" s="4"/>
     </row>
     <row r="76">
       <c r="A76" s="4"/>
@@ -49341,6 +49491,8 @@
       <c r="AD76" s="4"/>
       <c r="AE76" s="4"/>
       <c r="AF76" s="4"/>
+      <c r="AG76" s="4"/>
+      <c r="AH76" s="4"/>
     </row>
     <row r="77">
       <c r="A77" s="4"/>
@@ -49375,6 +49527,8 @@
       <c r="AD77" s="4"/>
       <c r="AE77" s="4"/>
       <c r="AF77" s="4"/>
+      <c r="AG77" s="4"/>
+      <c r="AH77" s="4"/>
     </row>
     <row r="78">
       <c r="A78" s="4"/>
@@ -49409,6 +49563,8 @@
       <c r="AD78" s="4"/>
       <c r="AE78" s="4"/>
       <c r="AF78" s="4"/>
+      <c r="AG78" s="4"/>
+      <c r="AH78" s="4"/>
     </row>
     <row r="79">
       <c r="A79" s="4"/>
@@ -49443,6 +49599,8 @@
       <c r="AD79" s="4"/>
       <c r="AE79" s="4"/>
       <c r="AF79" s="4"/>
+      <c r="AG79" s="4"/>
+      <c r="AH79" s="4"/>
     </row>
     <row r="80">
       <c r="A80" s="4"/>
@@ -49477,6 +49635,8 @@
       <c r="AD80" s="4"/>
       <c r="AE80" s="4"/>
       <c r="AF80" s="4"/>
+      <c r="AG80" s="4"/>
+      <c r="AH80" s="4"/>
     </row>
     <row r="81">
       <c r="A81" s="4"/>
@@ -49511,6 +49671,8 @@
       <c r="AD81" s="4"/>
       <c r="AE81" s="4"/>
       <c r="AF81" s="4"/>
+      <c r="AG81" s="4"/>
+      <c r="AH81" s="4"/>
     </row>
     <row r="82">
       <c r="A82" s="4"/>
@@ -49545,6 +49707,8 @@
       <c r="AD82" s="4"/>
       <c r="AE82" s="4"/>
       <c r="AF82" s="4"/>
+      <c r="AG82" s="4"/>
+      <c r="AH82" s="4"/>
     </row>
     <row r="83">
       <c r="A83" s="4"/>
@@ -49579,6 +49743,8 @@
       <c r="AD83" s="4"/>
       <c r="AE83" s="4"/>
       <c r="AF83" s="4"/>
+      <c r="AG83" s="4"/>
+      <c r="AH83" s="4"/>
     </row>
     <row r="84">
       <c r="A84" s="4"/>
@@ -49613,6 +49779,8 @@
       <c r="AD84" s="4"/>
       <c r="AE84" s="4"/>
       <c r="AF84" s="4"/>
+      <c r="AG84" s="4"/>
+      <c r="AH84" s="4"/>
     </row>
     <row r="85">
       <c r="A85" s="4"/>
@@ -49647,6 +49815,8 @@
       <c r="AD85" s="4"/>
       <c r="AE85" s="4"/>
       <c r="AF85" s="4"/>
+      <c r="AG85" s="4"/>
+      <c r="AH85" s="4"/>
     </row>
     <row r="86">
       <c r="A86" s="4"/>
@@ -49681,6 +49851,8 @@
       <c r="AD86" s="4"/>
       <c r="AE86" s="4"/>
       <c r="AF86" s="4"/>
+      <c r="AG86" s="4"/>
+      <c r="AH86" s="4"/>
     </row>
     <row r="87">
       <c r="A87" s="4"/>
@@ -49715,6 +49887,8 @@
       <c r="AD87" s="4"/>
       <c r="AE87" s="4"/>
       <c r="AF87" s="4"/>
+      <c r="AG87" s="4"/>
+      <c r="AH87" s="4"/>
     </row>
     <row r="88">
       <c r="A88" s="4"/>
@@ -49749,6 +49923,8 @@
       <c r="AD88" s="4"/>
       <c r="AE88" s="4"/>
       <c r="AF88" s="4"/>
+      <c r="AG88" s="4"/>
+      <c r="AH88" s="4"/>
     </row>
     <row r="89">
       <c r="A89" s="4"/>
@@ -49783,6 +49959,8 @@
       <c r="AD89" s="4"/>
       <c r="AE89" s="4"/>
       <c r="AF89" s="4"/>
+      <c r="AG89" s="4"/>
+      <c r="AH89" s="4"/>
     </row>
     <row r="90">
       <c r="A90" s="4"/>
@@ -49817,6 +49995,8 @@
       <c r="AD90" s="4"/>
       <c r="AE90" s="4"/>
       <c r="AF90" s="4"/>
+      <c r="AG90" s="4"/>
+      <c r="AH90" s="4"/>
     </row>
     <row r="91">
       <c r="A91" s="4"/>
@@ -49851,6 +50031,8 @@
       <c r="AD91" s="4"/>
       <c r="AE91" s="4"/>
       <c r="AF91" s="4"/>
+      <c r="AG91" s="4"/>
+      <c r="AH91" s="4"/>
     </row>
     <row r="92">
       <c r="A92" s="4"/>
@@ -49885,6 +50067,8 @@
       <c r="AD92" s="4"/>
       <c r="AE92" s="4"/>
       <c r="AF92" s="4"/>
+      <c r="AG92" s="4"/>
+      <c r="AH92" s="4"/>
     </row>
     <row r="93">
       <c r="A93" s="4"/>
@@ -49919,6 +50103,8 @@
       <c r="AD93" s="4"/>
       <c r="AE93" s="4"/>
       <c r="AF93" s="4"/>
+      <c r="AG93" s="4"/>
+      <c r="AH93" s="4"/>
     </row>
     <row r="94">
       <c r="A94" s="4"/>
@@ -49953,6 +50139,8 @@
       <c r="AD94" s="4"/>
       <c r="AE94" s="4"/>
       <c r="AF94" s="4"/>
+      <c r="AG94" s="4"/>
+      <c r="AH94" s="4"/>
     </row>
     <row r="95">
       <c r="A95" s="4"/>
@@ -49987,6 +50175,8 @@
       <c r="AD95" s="4"/>
       <c r="AE95" s="4"/>
       <c r="AF95" s="4"/>
+      <c r="AG95" s="4"/>
+      <c r="AH95" s="4"/>
     </row>
     <row r="96">
       <c r="A96" s="4"/>
@@ -50021,6 +50211,8 @@
       <c r="AD96" s="4"/>
       <c r="AE96" s="4"/>
       <c r="AF96" s="4"/>
+      <c r="AG96" s="4"/>
+      <c r="AH96" s="4"/>
     </row>
     <row r="97">
       <c r="A97" s="4"/>
@@ -50055,6 +50247,8 @@
       <c r="AD97" s="4"/>
       <c r="AE97" s="4"/>
       <c r="AF97" s="4"/>
+      <c r="AG97" s="4"/>
+      <c r="AH97" s="4"/>
     </row>
     <row r="98">
       <c r="A98" s="4"/>
@@ -50089,6 +50283,8 @@
       <c r="AD98" s="4"/>
       <c r="AE98" s="4"/>
       <c r="AF98" s="4"/>
+      <c r="AG98" s="4"/>
+      <c r="AH98" s="4"/>
     </row>
     <row r="99">
       <c r="A99" s="4"/>
@@ -50123,6 +50319,8 @@
       <c r="AD99" s="4"/>
       <c r="AE99" s="4"/>
       <c r="AF99" s="4"/>
+      <c r="AG99" s="4"/>
+      <c r="AH99" s="4"/>
     </row>
     <row r="100">
       <c r="A100" s="4"/>
@@ -50157,6 +50355,8 @@
       <c r="AD100" s="4"/>
       <c r="AE100" s="4"/>
       <c r="AF100" s="4"/>
+      <c r="AG100" s="4"/>
+      <c r="AH100" s="4"/>
     </row>
     <row r="101">
       <c r="A101" s="4"/>
@@ -50191,6 +50391,8 @@
       <c r="AD101" s="4"/>
       <c r="AE101" s="4"/>
       <c r="AF101" s="4"/>
+      <c r="AG101" s="4"/>
+      <c r="AH101" s="4"/>
     </row>
     <row r="102">
       <c r="A102" s="4"/>
@@ -50225,6 +50427,8 @@
       <c r="AD102" s="4"/>
       <c r="AE102" s="4"/>
       <c r="AF102" s="4"/>
+      <c r="AG102" s="4"/>
+      <c r="AH102" s="4"/>
     </row>
     <row r="103">
       <c r="A103" s="4"/>
@@ -50259,6 +50463,8 @@
       <c r="AD103" s="4"/>
       <c r="AE103" s="4"/>
       <c r="AF103" s="4"/>
+      <c r="AG103" s="4"/>
+      <c r="AH103" s="4"/>
     </row>
     <row r="104">
       <c r="A104" s="4"/>
@@ -50293,6 +50499,8 @@
       <c r="AD104" s="4"/>
       <c r="AE104" s="4"/>
       <c r="AF104" s="4"/>
+      <c r="AG104" s="4"/>
+      <c r="AH104" s="4"/>
     </row>
     <row r="105">
       <c r="A105" s="4"/>
@@ -50327,6 +50535,8 @@
       <c r="AD105" s="4"/>
       <c r="AE105" s="4"/>
       <c r="AF105" s="4"/>
+      <c r="AG105" s="4"/>
+      <c r="AH105" s="4"/>
     </row>
     <row r="106">
       <c r="A106" s="4"/>
@@ -50361,6 +50571,8 @@
       <c r="AD106" s="4"/>
       <c r="AE106" s="4"/>
       <c r="AF106" s="4"/>
+      <c r="AG106" s="4"/>
+      <c r="AH106" s="4"/>
     </row>
     <row r="107">
       <c r="A107" s="4"/>
@@ -50395,6 +50607,8 @@
       <c r="AD107" s="4"/>
       <c r="AE107" s="4"/>
       <c r="AF107" s="4"/>
+      <c r="AG107" s="4"/>
+      <c r="AH107" s="4"/>
     </row>
     <row r="108">
       <c r="A108" s="4"/>
@@ -50429,6 +50643,8 @@
       <c r="AD108" s="4"/>
       <c r="AE108" s="4"/>
       <c r="AF108" s="4"/>
+      <c r="AG108" s="4"/>
+      <c r="AH108" s="4"/>
     </row>
     <row r="109">
       <c r="A109" s="4"/>
@@ -50463,6 +50679,8 @@
       <c r="AD109" s="4"/>
       <c r="AE109" s="4"/>
       <c r="AF109" s="4"/>
+      <c r="AG109" s="4"/>
+      <c r="AH109" s="4"/>
     </row>
     <row r="110">
       <c r="A110" s="4"/>
@@ -50497,6 +50715,8 @@
       <c r="AD110" s="4"/>
       <c r="AE110" s="4"/>
       <c r="AF110" s="4"/>
+      <c r="AG110" s="4"/>
+      <c r="AH110" s="4"/>
     </row>
     <row r="111">
       <c r="A111" s="4"/>
@@ -50531,6 +50751,8 @@
       <c r="AD111" s="4"/>
       <c r="AE111" s="4"/>
       <c r="AF111" s="4"/>
+      <c r="AG111" s="4"/>
+      <c r="AH111" s="4"/>
     </row>
     <row r="112">
       <c r="A112" s="4"/>
@@ -50565,6 +50787,8 @@
       <c r="AD112" s="4"/>
       <c r="AE112" s="4"/>
       <c r="AF112" s="4"/>
+      <c r="AG112" s="4"/>
+      <c r="AH112" s="4"/>
     </row>
     <row r="113">
       <c r="A113" s="4"/>
@@ -50599,6 +50823,8 @@
       <c r="AD113" s="4"/>
       <c r="AE113" s="4"/>
       <c r="AF113" s="4"/>
+      <c r="AG113" s="4"/>
+      <c r="AH113" s="4"/>
     </row>
     <row r="114">
       <c r="A114" s="4"/>
@@ -50633,6 +50859,8 @@
       <c r="AD114" s="4"/>
       <c r="AE114" s="4"/>
       <c r="AF114" s="4"/>
+      <c r="AG114" s="4"/>
+      <c r="AH114" s="4"/>
     </row>
     <row r="115">
       <c r="A115" s="4"/>
@@ -50667,6 +50895,8 @@
       <c r="AD115" s="4"/>
       <c r="AE115" s="4"/>
       <c r="AF115" s="4"/>
+      <c r="AG115" s="4"/>
+      <c r="AH115" s="4"/>
     </row>
     <row r="116">
       <c r="A116" s="4"/>
@@ -50701,6 +50931,8 @@
       <c r="AD116" s="4"/>
       <c r="AE116" s="4"/>
       <c r="AF116" s="4"/>
+      <c r="AG116" s="4"/>
+      <c r="AH116" s="4"/>
     </row>
     <row r="117">
       <c r="A117" s="4"/>
@@ -50735,6 +50967,8 @@
       <c r="AD117" s="4"/>
       <c r="AE117" s="4"/>
       <c r="AF117" s="4"/>
+      <c r="AG117" s="4"/>
+      <c r="AH117" s="4"/>
     </row>
     <row r="118">
       <c r="A118" s="4"/>
@@ -50769,6 +51003,8 @@
       <c r="AD118" s="4"/>
       <c r="AE118" s="4"/>
       <c r="AF118" s="4"/>
+      <c r="AG118" s="4"/>
+      <c r="AH118" s="4"/>
     </row>
     <row r="119">
       <c r="A119" s="4"/>
@@ -50803,6 +51039,8 @@
       <c r="AD119" s="4"/>
       <c r="AE119" s="4"/>
       <c r="AF119" s="4"/>
+      <c r="AG119" s="4"/>
+      <c r="AH119" s="4"/>
     </row>
     <row r="120">
       <c r="A120" s="4"/>
@@ -50837,6 +51075,8 @@
       <c r="AD120" s="4"/>
       <c r="AE120" s="4"/>
       <c r="AF120" s="4"/>
+      <c r="AG120" s="4"/>
+      <c r="AH120" s="4"/>
     </row>
     <row r="121">
       <c r="A121" s="4"/>
@@ -50871,6 +51111,8 @@
       <c r="AD121" s="4"/>
       <c r="AE121" s="4"/>
       <c r="AF121" s="4"/>
+      <c r="AG121" s="4"/>
+      <c r="AH121" s="4"/>
     </row>
     <row r="122">
       <c r="A122" s="4"/>
@@ -50905,6 +51147,8 @@
       <c r="AD122" s="4"/>
       <c r="AE122" s="4"/>
       <c r="AF122" s="4"/>
+      <c r="AG122" s="4"/>
+      <c r="AH122" s="4"/>
     </row>
     <row r="123">
       <c r="A123" s="4"/>
@@ -50939,6 +51183,8 @@
       <c r="AD123" s="4"/>
       <c r="AE123" s="4"/>
       <c r="AF123" s="4"/>
+      <c r="AG123" s="4"/>
+      <c r="AH123" s="4"/>
     </row>
     <row r="124">
       <c r="A124" s="4"/>
@@ -50973,6 +51219,8 @@
       <c r="AD124" s="4"/>
       <c r="AE124" s="4"/>
       <c r="AF124" s="4"/>
+      <c r="AG124" s="4"/>
+      <c r="AH124" s="4"/>
     </row>
     <row r="125">
       <c r="A125" s="4"/>
@@ -51007,6 +51255,8 @@
       <c r="AD125" s="4"/>
       <c r="AE125" s="4"/>
       <c r="AF125" s="4"/>
+      <c r="AG125" s="4"/>
+      <c r="AH125" s="4"/>
     </row>
     <row r="126">
       <c r="A126" s="4"/>
@@ -51041,6 +51291,8 @@
       <c r="AD126" s="4"/>
       <c r="AE126" s="4"/>
       <c r="AF126" s="4"/>
+      <c r="AG126" s="4"/>
+      <c r="AH126" s="4"/>
     </row>
     <row r="127">
       <c r="A127" s="4"/>
@@ -51075,6 +51327,8 @@
       <c r="AD127" s="4"/>
       <c r="AE127" s="4"/>
       <c r="AF127" s="4"/>
+      <c r="AG127" s="4"/>
+      <c r="AH127" s="4"/>
     </row>
     <row r="128">
       <c r="A128" s="4"/>
@@ -51109,6 +51363,8 @@
       <c r="AD128" s="4"/>
       <c r="AE128" s="4"/>
       <c r="AF128" s="4"/>
+      <c r="AG128" s="4"/>
+      <c r="AH128" s="4"/>
     </row>
     <row r="129">
       <c r="A129" s="4"/>
@@ -51143,6 +51399,8 @@
       <c r="AD129" s="4"/>
       <c r="AE129" s="4"/>
       <c r="AF129" s="4"/>
+      <c r="AG129" s="4"/>
+      <c r="AH129" s="4"/>
     </row>
     <row r="130">
       <c r="A130" s="4"/>
@@ -51177,6 +51435,8 @@
       <c r="AD130" s="4"/>
       <c r="AE130" s="4"/>
       <c r="AF130" s="4"/>
+      <c r="AG130" s="4"/>
+      <c r="AH130" s="4"/>
     </row>
     <row r="131">
       <c r="A131" s="4"/>
@@ -51211,6 +51471,8 @@
       <c r="AD131" s="4"/>
       <c r="AE131" s="4"/>
       <c r="AF131" s="4"/>
+      <c r="AG131" s="4"/>
+      <c r="AH131" s="4"/>
     </row>
     <row r="132">
       <c r="A132" s="4"/>
@@ -51245,6 +51507,8 @@
       <c r="AD132" s="4"/>
       <c r="AE132" s="4"/>
       <c r="AF132" s="4"/>
+      <c r="AG132" s="4"/>
+      <c r="AH132" s="4"/>
     </row>
     <row r="133">
       <c r="A133" s="4"/>
@@ -51279,6 +51543,8 @@
       <c r="AD133" s="4"/>
       <c r="AE133" s="4"/>
       <c r="AF133" s="4"/>
+      <c r="AG133" s="4"/>
+      <c r="AH133" s="4"/>
     </row>
     <row r="134">
       <c r="A134" s="4"/>
@@ -51313,6 +51579,8 @@
       <c r="AD134" s="4"/>
       <c r="AE134" s="4"/>
       <c r="AF134" s="4"/>
+      <c r="AG134" s="4"/>
+      <c r="AH134" s="4"/>
     </row>
     <row r="135">
       <c r="A135" s="4"/>
@@ -51347,6 +51615,8 @@
       <c r="AD135" s="4"/>
       <c r="AE135" s="4"/>
       <c r="AF135" s="4"/>
+      <c r="AG135" s="4"/>
+      <c r="AH135" s="4"/>
     </row>
     <row r="136">
       <c r="A136" s="4"/>
@@ -51381,6 +51651,8 @@
       <c r="AD136" s="4"/>
       <c r="AE136" s="4"/>
       <c r="AF136" s="4"/>
+      <c r="AG136" s="4"/>
+      <c r="AH136" s="4"/>
     </row>
     <row r="137">
       <c r="A137" s="4"/>
@@ -51415,6 +51687,8 @@
       <c r="AD137" s="4"/>
       <c r="AE137" s="4"/>
       <c r="AF137" s="4"/>
+      <c r="AG137" s="4"/>
+      <c r="AH137" s="4"/>
     </row>
     <row r="138">
       <c r="A138" s="4"/>
@@ -51449,6 +51723,8 @@
       <c r="AD138" s="4"/>
       <c r="AE138" s="4"/>
       <c r="AF138" s="4"/>
+      <c r="AG138" s="4"/>
+      <c r="AH138" s="4"/>
     </row>
     <row r="139">
       <c r="A139" s="4"/>
@@ -51483,6 +51759,8 @@
       <c r="AD139" s="4"/>
       <c r="AE139" s="4"/>
       <c r="AF139" s="4"/>
+      <c r="AG139" s="4"/>
+      <c r="AH139" s="4"/>
     </row>
     <row r="140">
       <c r="A140" s="4"/>
@@ -51517,6 +51795,8 @@
       <c r="AD140" s="4"/>
       <c r="AE140" s="4"/>
       <c r="AF140" s="4"/>
+      <c r="AG140" s="4"/>
+      <c r="AH140" s="4"/>
     </row>
     <row r="141">
       <c r="A141" s="4"/>
@@ -51551,6 +51831,8 @@
       <c r="AD141" s="4"/>
       <c r="AE141" s="4"/>
       <c r="AF141" s="4"/>
+      <c r="AG141" s="4"/>
+      <c r="AH141" s="4"/>
     </row>
     <row r="142">
       <c r="A142" s="4"/>
@@ -51585,6 +51867,8 @@
       <c r="AD142" s="4"/>
       <c r="AE142" s="4"/>
       <c r="AF142" s="4"/>
+      <c r="AG142" s="4"/>
+      <c r="AH142" s="4"/>
     </row>
     <row r="143">
       <c r="A143" s="4"/>
@@ -51619,6 +51903,8 @@
       <c r="AD143" s="4"/>
       <c r="AE143" s="4"/>
       <c r="AF143" s="4"/>
+      <c r="AG143" s="4"/>
+      <c r="AH143" s="4"/>
     </row>
     <row r="144">
       <c r="A144" s="4"/>
@@ -51653,6 +51939,8 @@
       <c r="AD144" s="4"/>
       <c r="AE144" s="4"/>
       <c r="AF144" s="4"/>
+      <c r="AG144" s="4"/>
+      <c r="AH144" s="4"/>
     </row>
     <row r="145">
       <c r="A145" s="4"/>
@@ -51687,6 +51975,8 @@
       <c r="AD145" s="4"/>
       <c r="AE145" s="4"/>
       <c r="AF145" s="4"/>
+      <c r="AG145" s="4"/>
+      <c r="AH145" s="4"/>
     </row>
     <row r="146">
       <c r="A146" s="4"/>
@@ -51721,6 +52011,8 @@
       <c r="AD146" s="4"/>
       <c r="AE146" s="4"/>
       <c r="AF146" s="4"/>
+      <c r="AG146" s="4"/>
+      <c r="AH146" s="4"/>
     </row>
     <row r="147">
       <c r="A147" s="4"/>
@@ -51755,6 +52047,8 @@
       <c r="AD147" s="4"/>
       <c r="AE147" s="4"/>
       <c r="AF147" s="4"/>
+      <c r="AG147" s="4"/>
+      <c r="AH147" s="4"/>
     </row>
     <row r="148">
       <c r="A148" s="4"/>
@@ -51789,6 +52083,8 @@
       <c r="AD148" s="4"/>
       <c r="AE148" s="4"/>
       <c r="AF148" s="4"/>
+      <c r="AG148" s="4"/>
+      <c r="AH148" s="4"/>
     </row>
     <row r="149">
       <c r="A149" s="4"/>
@@ -51823,6 +52119,8 @@
       <c r="AD149" s="4"/>
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
+      <c r="AG149" s="4"/>
+      <c r="AH149" s="4"/>
     </row>
     <row r="150">
       <c r="A150" s="4"/>
@@ -51857,6 +52155,8 @@
       <c r="AD150" s="4"/>
       <c r="AE150" s="4"/>
       <c r="AF150" s="4"/>
+      <c r="AG150" s="4"/>
+      <c r="AH150" s="4"/>
     </row>
     <row r="151">
       <c r="A151" s="4"/>
@@ -51891,6 +52191,8 @@
       <c r="AD151" s="4"/>
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
+      <c r="AG151" s="4"/>
+      <c r="AH151" s="4"/>
     </row>
     <row r="152">
       <c r="A152" s="4"/>
@@ -51925,6 +52227,8 @@
       <c r="AD152" s="4"/>
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
+      <c r="AG152" s="4"/>
+      <c r="AH152" s="4"/>
     </row>
     <row r="153">
       <c r="A153" s="4"/>
@@ -51959,6 +52263,8 @@
       <c r="AD153" s="4"/>
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
+      <c r="AG153" s="4"/>
+      <c r="AH153" s="4"/>
     </row>
     <row r="154">
       <c r="A154" s="4"/>
@@ -51993,6 +52299,8 @@
       <c r="AD154" s="4"/>
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
+      <c r="AG154" s="4"/>
+      <c r="AH154" s="4"/>
     </row>
     <row r="155">
       <c r="A155" s="4"/>
@@ -52027,6 +52335,8 @@
       <c r="AD155" s="4"/>
       <c r="AE155" s="4"/>
       <c r="AF155" s="4"/>
+      <c r="AG155" s="4"/>
+      <c r="AH155" s="4"/>
     </row>
     <row r="156">
       <c r="A156" s="4"/>
@@ -52061,6 +52371,8 @@
       <c r="AD156" s="4"/>
       <c r="AE156" s="4"/>
       <c r="AF156" s="4"/>
+      <c r="AG156" s="4"/>
+      <c r="AH156" s="4"/>
     </row>
     <row r="157">
       <c r="A157" s="4"/>
@@ -52095,6 +52407,8 @@
       <c r="AD157" s="4"/>
       <c r="AE157" s="4"/>
       <c r="AF157" s="4"/>
+      <c r="AG157" s="4"/>
+      <c r="AH157" s="4"/>
     </row>
     <row r="158">
       <c r="A158" s="4"/>
@@ -52129,6 +52443,8 @@
       <c r="AD158" s="4"/>
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
+      <c r="AG158" s="4"/>
+      <c r="AH158" s="4"/>
     </row>
     <row r="159">
       <c r="A159" s="4"/>
@@ -52163,6 +52479,8 @@
       <c r="AD159" s="4"/>
       <c r="AE159" s="4"/>
       <c r="AF159" s="4"/>
+      <c r="AG159" s="4"/>
+      <c r="AH159" s="4"/>
     </row>
     <row r="160">
       <c r="A160" s="4"/>
@@ -52197,6 +52515,8 @@
       <c r="AD160" s="4"/>
       <c r="AE160" s="4"/>
       <c r="AF160" s="4"/>
+      <c r="AG160" s="4"/>
+      <c r="AH160" s="4"/>
     </row>
     <row r="161">
       <c r="A161" s="4"/>
@@ -52231,6 +52551,8 @@
       <c r="AD161" s="4"/>
       <c r="AE161" s="4"/>
       <c r="AF161" s="4"/>
+      <c r="AG161" s="4"/>
+      <c r="AH161" s="4"/>
     </row>
     <row r="162">
       <c r="A162" s="4"/>
@@ -52265,6 +52587,8 @@
       <c r="AD162" s="4"/>
       <c r="AE162" s="4"/>
       <c r="AF162" s="4"/>
+      <c r="AG162" s="4"/>
+      <c r="AH162" s="4"/>
     </row>
     <row r="163">
       <c r="A163" s="4"/>
@@ -52299,6 +52623,8 @@
       <c r="AD163" s="4"/>
       <c r="AE163" s="4"/>
       <c r="AF163" s="4"/>
+      <c r="AG163" s="4"/>
+      <c r="AH163" s="4"/>
     </row>
     <row r="164">
       <c r="A164" s="4"/>
@@ -52333,6 +52659,8 @@
       <c r="AD164" s="4"/>
       <c r="AE164" s="4"/>
       <c r="AF164" s="4"/>
+      <c r="AG164" s="4"/>
+      <c r="AH164" s="4"/>
     </row>
     <row r="165">
       <c r="A165" s="4"/>
@@ -52367,6 +52695,8 @@
       <c r="AD165" s="4"/>
       <c r="AE165" s="4"/>
       <c r="AF165" s="4"/>
+      <c r="AG165" s="4"/>
+      <c r="AH165" s="4"/>
     </row>
     <row r="166">
       <c r="A166" s="4"/>
@@ -52401,6 +52731,8 @@
       <c r="AD166" s="4"/>
       <c r="AE166" s="4"/>
       <c r="AF166" s="4"/>
+      <c r="AG166" s="4"/>
+      <c r="AH166" s="4"/>
     </row>
     <row r="167">
       <c r="A167" s="4"/>
@@ -52435,6 +52767,8 @@
       <c r="AD167" s="4"/>
       <c r="AE167" s="4"/>
       <c r="AF167" s="4"/>
+      <c r="AG167" s="4"/>
+      <c r="AH167" s="4"/>
     </row>
     <row r="168">
       <c r="A168" s="4"/>
@@ -52469,6 +52803,8 @@
       <c r="AD168" s="4"/>
       <c r="AE168" s="4"/>
       <c r="AF168" s="4"/>
+      <c r="AG168" s="4"/>
+      <c r="AH168" s="4"/>
     </row>
     <row r="169">
       <c r="A169" s="4"/>
@@ -52503,6 +52839,8 @@
       <c r="AD169" s="4"/>
       <c r="AE169" s="4"/>
       <c r="AF169" s="4"/>
+      <c r="AG169" s="4"/>
+      <c r="AH169" s="4"/>
     </row>
     <row r="170">
       <c r="A170" s="4"/>
@@ -52537,6 +52875,8 @@
       <c r="AD170" s="4"/>
       <c r="AE170" s="4"/>
       <c r="AF170" s="4"/>
+      <c r="AG170" s="4"/>
+      <c r="AH170" s="4"/>
     </row>
     <row r="171">
       <c r="A171" s="4"/>
@@ -52571,6 +52911,8 @@
       <c r="AD171" s="4"/>
       <c r="AE171" s="4"/>
       <c r="AF171" s="4"/>
+      <c r="AG171" s="4"/>
+      <c r="AH171" s="4"/>
     </row>
     <row r="172">
       <c r="A172" s="4"/>
@@ -52605,6 +52947,8 @@
       <c r="AD172" s="4"/>
       <c r="AE172" s="4"/>
       <c r="AF172" s="4"/>
+      <c r="AG172" s="4"/>
+      <c r="AH172" s="4"/>
     </row>
     <row r="173">
       <c r="A173" s="4"/>
@@ -52639,6 +52983,8 @@
       <c r="AD173" s="4"/>
       <c r="AE173" s="4"/>
       <c r="AF173" s="4"/>
+      <c r="AG173" s="4"/>
+      <c r="AH173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="4"/>
@@ -52673,6 +53019,8 @@
       <c r="AD174" s="4"/>
       <c r="AE174" s="4"/>
       <c r="AF174" s="4"/>
+      <c r="AG174" s="4"/>
+      <c r="AH174" s="4"/>
     </row>
     <row r="175">
       <c r="A175" s="4"/>
@@ -52707,6 +53055,8 @@
       <c r="AD175" s="4"/>
       <c r="AE175" s="4"/>
       <c r="AF175" s="4"/>
+      <c r="AG175" s="4"/>
+      <c r="AH175" s="4"/>
     </row>
     <row r="176">
       <c r="A176" s="4"/>
@@ -52741,6 +53091,8 @@
       <c r="AD176" s="4"/>
       <c r="AE176" s="4"/>
       <c r="AF176" s="4"/>
+      <c r="AG176" s="4"/>
+      <c r="AH176" s="4"/>
     </row>
     <row r="177">
       <c r="A177" s="4"/>
@@ -52775,6 +53127,8 @@
       <c r="AD177" s="4"/>
       <c r="AE177" s="4"/>
       <c r="AF177" s="4"/>
+      <c r="AG177" s="4"/>
+      <c r="AH177" s="4"/>
     </row>
     <row r="178">
       <c r="A178" s="4"/>
@@ -52809,6 +53163,8 @@
       <c r="AD178" s="4"/>
       <c r="AE178" s="4"/>
       <c r="AF178" s="4"/>
+      <c r="AG178" s="4"/>
+      <c r="AH178" s="4"/>
     </row>
     <row r="179">
       <c r="A179" s="4"/>
@@ -52843,6 +53199,8 @@
       <c r="AD179" s="4"/>
       <c r="AE179" s="4"/>
       <c r="AF179" s="4"/>
+      <c r="AG179" s="4"/>
+      <c r="AH179" s="4"/>
     </row>
     <row r="180">
       <c r="A180" s="4"/>
@@ -52877,6 +53235,8 @@
       <c r="AD180" s="4"/>
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
+      <c r="AG180" s="4"/>
+      <c r="AH180" s="4"/>
     </row>
     <row r="181">
       <c r="A181" s="4"/>
@@ -52911,6 +53271,8 @@
       <c r="AD181" s="4"/>
       <c r="AE181" s="4"/>
       <c r="AF181" s="4"/>
+      <c r="AG181" s="4"/>
+      <c r="AH181" s="4"/>
     </row>
     <row r="182">
       <c r="A182" s="4"/>
@@ -52945,6 +53307,8 @@
       <c r="AD182" s="4"/>
       <c r="AE182" s="4"/>
       <c r="AF182" s="4"/>
+      <c r="AG182" s="4"/>
+      <c r="AH182" s="4"/>
     </row>
     <row r="183">
       <c r="A183" s="4"/>
@@ -52979,6 +53343,8 @@
       <c r="AD183" s="4"/>
       <c r="AE183" s="4"/>
       <c r="AF183" s="4"/>
+      <c r="AG183" s="4"/>
+      <c r="AH183" s="4"/>
     </row>
     <row r="184">
       <c r="A184" s="4"/>
@@ -53013,6 +53379,8 @@
       <c r="AD184" s="4"/>
       <c r="AE184" s="4"/>
       <c r="AF184" s="4"/>
+      <c r="AG184" s="4"/>
+      <c r="AH184" s="4"/>
     </row>
     <row r="185">
       <c r="A185" s="4"/>
@@ -53047,6 +53415,8 @@
       <c r="AD185" s="4"/>
       <c r="AE185" s="4"/>
       <c r="AF185" s="4"/>
+      <c r="AG185" s="4"/>
+      <c r="AH185" s="4"/>
     </row>
     <row r="186">
       <c r="A186" s="4"/>
@@ -53081,6 +53451,8 @@
       <c r="AD186" s="4"/>
       <c r="AE186" s="4"/>
       <c r="AF186" s="4"/>
+      <c r="AG186" s="4"/>
+      <c r="AH186" s="4"/>
     </row>
     <row r="187">
       <c r="A187" s="4"/>
@@ -53115,6 +53487,8 @@
       <c r="AD187" s="4"/>
       <c r="AE187" s="4"/>
       <c r="AF187" s="4"/>
+      <c r="AG187" s="4"/>
+      <c r="AH187" s="4"/>
     </row>
     <row r="188">
       <c r="A188" s="4"/>
@@ -53149,6 +53523,8 @@
       <c r="AD188" s="4"/>
       <c r="AE188" s="4"/>
       <c r="AF188" s="4"/>
+      <c r="AG188" s="4"/>
+      <c r="AH188" s="4"/>
     </row>
     <row r="189">
       <c r="A189" s="4"/>
@@ -53183,6 +53559,8 @@
       <c r="AD189" s="4"/>
       <c r="AE189" s="4"/>
       <c r="AF189" s="4"/>
+      <c r="AG189" s="4"/>
+      <c r="AH189" s="4"/>
     </row>
     <row r="190">
       <c r="A190" s="4"/>
@@ -53217,6 +53595,8 @@
       <c r="AD190" s="4"/>
       <c r="AE190" s="4"/>
       <c r="AF190" s="4"/>
+      <c r="AG190" s="4"/>
+      <c r="AH190" s="4"/>
     </row>
     <row r="191">
       <c r="A191" s="4"/>
@@ -53251,6 +53631,8 @@
       <c r="AD191" s="4"/>
       <c r="AE191" s="4"/>
       <c r="AF191" s="4"/>
+      <c r="AG191" s="4"/>
+      <c r="AH191" s="4"/>
     </row>
     <row r="192">
       <c r="A192" s="4"/>
@@ -53285,6 +53667,8 @@
       <c r="AD192" s="4"/>
       <c r="AE192" s="4"/>
       <c r="AF192" s="4"/>
+      <c r="AG192" s="4"/>
+      <c r="AH192" s="4"/>
     </row>
     <row r="193">
       <c r="A193" s="4"/>
@@ -53319,6 +53703,8 @@
       <c r="AD193" s="4"/>
       <c r="AE193" s="4"/>
       <c r="AF193" s="4"/>
+      <c r="AG193" s="4"/>
+      <c r="AH193" s="4"/>
     </row>
     <row r="194">
       <c r="A194" s="4"/>
@@ -53353,6 +53739,8 @@
       <c r="AD194" s="4"/>
       <c r="AE194" s="4"/>
       <c r="AF194" s="4"/>
+      <c r="AG194" s="4"/>
+      <c r="AH194" s="4"/>
     </row>
     <row r="195">
       <c r="A195" s="4"/>
@@ -53387,6 +53775,8 @@
       <c r="AD195" s="4"/>
       <c r="AE195" s="4"/>
       <c r="AF195" s="4"/>
+      <c r="AG195" s="4"/>
+      <c r="AH195" s="4"/>
     </row>
     <row r="196">
       <c r="A196" s="4"/>
@@ -53421,6 +53811,8 @@
       <c r="AD196" s="4"/>
       <c r="AE196" s="4"/>
       <c r="AF196" s="4"/>
+      <c r="AG196" s="4"/>
+      <c r="AH196" s="4"/>
     </row>
     <row r="197">
       <c r="A197" s="4"/>
@@ -53455,6 +53847,8 @@
       <c r="AD197" s="4"/>
       <c r="AE197" s="4"/>
       <c r="AF197" s="4"/>
+      <c r="AG197" s="4"/>
+      <c r="AH197" s="4"/>
     </row>
     <row r="198">
       <c r="A198" s="4"/>
@@ -53489,6 +53883,8 @@
       <c r="AD198" s="4"/>
       <c r="AE198" s="4"/>
       <c r="AF198" s="4"/>
+      <c r="AG198" s="4"/>
+      <c r="AH198" s="4"/>
     </row>
     <row r="199">
       <c r="A199" s="4"/>
@@ -53523,6 +53919,8 @@
       <c r="AD199" s="4"/>
       <c r="AE199" s="4"/>
       <c r="AF199" s="4"/>
+      <c r="AG199" s="4"/>
+      <c r="AH199" s="4"/>
     </row>
     <row r="200">
       <c r="A200" s="4"/>
@@ -53557,6 +53955,8 @@
       <c r="AD200" s="4"/>
       <c r="AE200" s="4"/>
       <c r="AF200" s="4"/>
+      <c r="AG200" s="4"/>
+      <c r="AH200" s="4"/>
     </row>
     <row r="201">
       <c r="A201" s="4"/>
@@ -53591,6 +53991,8 @@
       <c r="AD201" s="4"/>
       <c r="AE201" s="4"/>
       <c r="AF201" s="4"/>
+      <c r="AG201" s="4"/>
+      <c r="AH201" s="4"/>
     </row>
     <row r="202">
       <c r="A202" s="4"/>
@@ -53625,6 +54027,8 @@
       <c r="AD202" s="4"/>
       <c r="AE202" s="4"/>
       <c r="AF202" s="4"/>
+      <c r="AG202" s="4"/>
+      <c r="AH202" s="4"/>
     </row>
     <row r="203">
       <c r="A203" s="4"/>
@@ -53659,6 +54063,8 @@
       <c r="AD203" s="4"/>
       <c r="AE203" s="4"/>
       <c r="AF203" s="4"/>
+      <c r="AG203" s="4"/>
+      <c r="AH203" s="4"/>
     </row>
     <row r="204">
       <c r="A204" s="4"/>
@@ -53693,6 +54099,8 @@
       <c r="AD204" s="4"/>
       <c r="AE204" s="4"/>
       <c r="AF204" s="4"/>
+      <c r="AG204" s="4"/>
+      <c r="AH204" s="4"/>
     </row>
     <row r="205">
       <c r="A205" s="4"/>
@@ -53727,6 +54135,8 @@
       <c r="AD205" s="4"/>
       <c r="AE205" s="4"/>
       <c r="AF205" s="4"/>
+      <c r="AG205" s="4"/>
+      <c r="AH205" s="4"/>
     </row>
     <row r="206">
       <c r="A206" s="4"/>
@@ -53761,6 +54171,8 @@
       <c r="AD206" s="4"/>
       <c r="AE206" s="4"/>
       <c r="AF206" s="4"/>
+      <c r="AG206" s="4"/>
+      <c r="AH206" s="4"/>
     </row>
     <row r="207">
       <c r="A207" s="4"/>
@@ -53795,6 +54207,8 @@
       <c r="AD207" s="4"/>
       <c r="AE207" s="4"/>
       <c r="AF207" s="4"/>
+      <c r="AG207" s="4"/>
+      <c r="AH207" s="4"/>
     </row>
     <row r="208">
       <c r="A208" s="4"/>
@@ -53829,6 +54243,8 @@
       <c r="AD208" s="4"/>
       <c r="AE208" s="4"/>
       <c r="AF208" s="4"/>
+      <c r="AG208" s="4"/>
+      <c r="AH208" s="4"/>
     </row>
     <row r="209">
       <c r="A209" s="4"/>
@@ -53863,6 +54279,8 @@
       <c r="AD209" s="4"/>
       <c r="AE209" s="4"/>
       <c r="AF209" s="4"/>
+      <c r="AG209" s="4"/>
+      <c r="AH209" s="4"/>
     </row>
     <row r="210">
       <c r="A210" s="4"/>
@@ -53897,6 +54315,8 @@
       <c r="AD210" s="4"/>
       <c r="AE210" s="4"/>
       <c r="AF210" s="4"/>
+      <c r="AG210" s="4"/>
+      <c r="AH210" s="4"/>
     </row>
     <row r="211">
       <c r="A211" s="4"/>
@@ -53931,6 +54351,8 @@
       <c r="AD211" s="4"/>
       <c r="AE211" s="4"/>
       <c r="AF211" s="4"/>
+      <c r="AG211" s="4"/>
+      <c r="AH211" s="4"/>
     </row>
     <row r="212">
       <c r="A212" s="4"/>
@@ -53965,6 +54387,8 @@
       <c r="AD212" s="4"/>
       <c r="AE212" s="4"/>
       <c r="AF212" s="4"/>
+      <c r="AG212" s="4"/>
+      <c r="AH212" s="4"/>
     </row>
     <row r="213">
       <c r="A213" s="4"/>
@@ -53999,6 +54423,8 @@
       <c r="AD213" s="4"/>
       <c r="AE213" s="4"/>
       <c r="AF213" s="4"/>
+      <c r="AG213" s="4"/>
+      <c r="AH213" s="4"/>
     </row>
     <row r="214">
       <c r="A214" s="4"/>
@@ -54033,6 +54459,8 @@
       <c r="AD214" s="4"/>
       <c r="AE214" s="4"/>
       <c r="AF214" s="4"/>
+      <c r="AG214" s="4"/>
+      <c r="AH214" s="4"/>
     </row>
     <row r="215">
       <c r="A215" s="4"/>
@@ -54067,6 +54495,8 @@
       <c r="AD215" s="4"/>
       <c r="AE215" s="4"/>
       <c r="AF215" s="4"/>
+      <c r="AG215" s="4"/>
+      <c r="AH215" s="4"/>
     </row>
     <row r="216">
       <c r="A216" s="4"/>
@@ -54101,6 +54531,8 @@
       <c r="AD216" s="4"/>
       <c r="AE216" s="4"/>
       <c r="AF216" s="4"/>
+      <c r="AG216" s="4"/>
+      <c r="AH216" s="4"/>
     </row>
     <row r="217">
       <c r="A217" s="4"/>
@@ -54135,6 +54567,8 @@
       <c r="AD217" s="4"/>
       <c r="AE217" s="4"/>
       <c r="AF217" s="4"/>
+      <c r="AG217" s="4"/>
+      <c r="AH217" s="4"/>
     </row>
     <row r="218">
       <c r="A218" s="4"/>
@@ -54169,6 +54603,8 @@
       <c r="AD218" s="4"/>
       <c r="AE218" s="4"/>
       <c r="AF218" s="4"/>
+      <c r="AG218" s="4"/>
+      <c r="AH218" s="4"/>
     </row>
     <row r="219">
       <c r="A219" s="4"/>
@@ -54203,6 +54639,8 @@
       <c r="AD219" s="4"/>
       <c r="AE219" s="4"/>
       <c r="AF219" s="4"/>
+      <c r="AG219" s="4"/>
+      <c r="AH219" s="4"/>
     </row>
     <row r="220">
       <c r="A220" s="4"/>
@@ -54237,6 +54675,8 @@
       <c r="AD220" s="4"/>
       <c r="AE220" s="4"/>
       <c r="AF220" s="4"/>
+      <c r="AG220" s="4"/>
+      <c r="AH220" s="4"/>
     </row>
     <row r="221">
       <c r="B221" s="15"/>
